--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:37</t>
+    <t xml:space="preserve">2026-09-09 22:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:22</t>
+    <t xml:space="preserve">2026-09-12 19:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:39</t>
+    <t xml:space="preserve">2026-09-24 00:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:16</t>
+    <t xml:space="preserve">2026-09-27 22:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:06</t>
+    <t xml:space="preserve">2026-09-29 11:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -523,7 +523,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>27.27</v>
+        <v>272.71</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>19.11</v>
+        <v>191.15</v>
       </c>
     </row>
     <row r="4">
@@ -557,7 +557,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>18.79</v>
+        <v>187.9</v>
       </c>
     </row>
     <row r="5">
@@ -574,7 +574,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16.5</v>
+        <v>164.98</v>
       </c>
     </row>
     <row r="6">
@@ -591,7 +591,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>16.4</v>
+        <v>164.01</v>
       </c>
     </row>
     <row r="7">
@@ -608,7 +608,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>15.2</v>
+        <v>152.03</v>
       </c>
     </row>
     <row r="8">
@@ -625,7 +625,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>14.71</v>
+        <v>147.09</v>
       </c>
     </row>
     <row r="9">
@@ -642,7 +642,7 @@
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>14.69</v>
+        <v>146.88</v>
       </c>
     </row>
     <row r="10">
@@ -659,7 +659,7 @@
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>14.12</v>
+        <v>141.16</v>
       </c>
     </row>
     <row r="11">
@@ -676,7 +676,7 @@
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>14.09</v>
+        <v>140.9</v>
       </c>
     </row>
     <row r="12">
@@ -693,7 +693,7 @@
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12.48</v>
+        <v>124.83</v>
       </c>
     </row>
     <row r="13">
@@ -710,7 +710,7 @@
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12.34</v>
+        <v>123.39</v>
       </c>
     </row>
     <row r="14">
@@ -727,7 +727,7 @@
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>9.97</v>
+        <v>99.66</v>
       </c>
     </row>
     <row r="15">
@@ -744,7 +744,7 @@
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>9.42</v>
+        <v>94.23</v>
       </c>
     </row>
     <row r="16">
@@ -761,7 +761,7 @@
         <v>2021</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>8.86</v>
+        <v>88.63</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:00</t>
+    <t xml:space="preserve">2026-10-01 19:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:25</t>
+    <t xml:space="preserve">2026-10-02 13:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:05</t>
+    <t xml:space="preserve">2026-10-04 07:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 07:56</t>
+    <t xml:space="preserve">2026-10-05 07:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
